--- a/outputs/llm_eval/test_yjx/mul/two_turns/all35_correlation_results.xlsx
+++ b/outputs/llm_eval/test_yjx/mul/two_turns/all35_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.4375169146127993</v>
+        <v>0.4010093573401639</v>
       </c>
       <c r="C2">
-        <v>0.4257776026554733</v>
+        <v>0.3957006772256033</v>
       </c>
       <c r="D2">
-        <v>0.3697214824427004</v>
+        <v>0.3577127178421569</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.3639876065596777</v>
+        <v>0.3194254552958848</v>
       </c>
       <c r="C3">
-        <v>0.4114423991460202</v>
+        <v>0.3722498651800374</v>
       </c>
       <c r="D3">
-        <v>0.3042053770291618</v>
+        <v>0.2799132112364768</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.4850526661014054</v>
+        <v>0.4455129334834567</v>
       </c>
       <c r="C4">
-        <v>0.499978260320649</v>
+        <v>0.4746689063374386</v>
       </c>
       <c r="D4">
-        <v>0.3877685807803314</v>
+        <v>0.3719169113008777</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.496753712371676</v>
+        <v>0.4925124736613733</v>
       </c>
       <c r="C5">
-        <v>0.4947571750021972</v>
+        <v>0.4977968567682488</v>
       </c>
       <c r="D5">
-        <v>0.3958062473824706</v>
+        <v>0.40935503200233</v>
       </c>
     </row>
   </sheetData>
